--- a/extenbooks/XS1502.xlsx
+++ b/extenbooks/XS1502.xlsx
@@ -447,22 +447,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="53" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>XS1502 — Managerial Unproductive Labor (Mohun 2013)</t>
+          <t>XS1502 — Supervisory Employment Share (Mohun 2014)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE, units=thousands_workers</t>
+          <t>Mohun 2014, RRPE 46(3):355-379, units=share</t>
         </is>
       </c>
     </row>
@@ -480,338 +480,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1948</v>
+        <v>1964</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7669.354685365971</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1949</v>
+        <v>1991</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8395.97896522213</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8822.320611249512</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9507.614863469011</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>9768.446635844581</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>9910.669328857928</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>10234.76218540804</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>10299.70772447557</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1956</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>11025.29945430302</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>11854.5056043941</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>12607.58173603176</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>13329.24873356444</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>14347.08151496417</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>14746.79159652223</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>14969.92245757772</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>15550.9798600152</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>15321.64804277195</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>15501.4561553119</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>16052.6582041263</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>17343.37571447416</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>18175.2315310317</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>19180.86796480512</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>20035.545468397</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>20370.8961992076</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>21316.79010716228</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>20750.56916112193</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>21041.99875597388</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>20887.89576794697</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>21688.49591795224</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>22095.96186951507</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>23058.7904819594</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>25590.49437322</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>26129.83812957805</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>26813.3081002641</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>26485.23878560075</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>27155.96078107397</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>26969.01060575966</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>26865.96142252883</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>27580.15419409015</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>28298.2595006567</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>30389.2013916098</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>31307.36638816474</v>
+        <v>0.179</v>
       </c>
     </row>
   </sheetData>
@@ -825,11 +513,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Managerial Unproductive Labor (Mohun 2013)</t>
+          <t>Supervisory Employment Share (Mohun 2014)</t>
         </is>
       </c>
     </row>
@@ -896,7 +584,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>thousands_workers</t>
+          <t>share</t>
         </is>
       </c>
     </row>
@@ -920,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1989</t>
+          <t>1964-2010</t>
         </is>
       </c>
     </row>
@@ -997,7 +685,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE</t>
+          <t>Mohun 2014, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1014,19 +702,23 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t># XS1502 — Managerial Unproductive Labor (Mohun 2013)</t>
+          <t>&gt; **D4 REBUILD (2026-07-02) — SUPERSEDES the text below (pending D5 doc-regen).**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: supervisory (managers+capitalists) SHARE of total employment (Mohun 2013 Fig 3): 1964=16.8%, peak 1991=19.9%, 2010=17.9%.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>&gt; Units are now a **share/ratio over 1964-2010** (benchmark anchors, table/text-grade), NOT</t>
         </is>
       </c>
     </row>
@@ -1034,17 +726,73 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt; thousands of FTE over 1948-1989. The old 1948-1989 thousands series was a mislabeled</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>&gt; Attribution: **Mohun (2014), RRPE 46(3):355-379**, DOI 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&gt; Source: `data/source/external_studies/mohun_2013_published_shares.csv`. See D4 report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t># XS1502 — Managerial Unproductive Labor (Mohun 2013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1061,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1094,12 +842,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes supervisory (managers-plus-capitalists) unproductive labor ONLY as SHARES (Figure 3), never as a year-by-year FTE-level table. Verbatim published anchors: supervisory EMPLOYMENT share 1964 = 16.8% of total employment, peak 1991 = 19.9%, 2010 = 17.9%; WAGE share 1964 = ~32% of total wages, peak 2007 = 47.8%, 2010 = 46.6%. HONESTY NOTE: the shipped XS1502 series (source column Lum_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 supervisory / total-employment ratio is 24.4%, which does NOT reproduce Mohun's published 16.8% (the shipped split puts far more of Lu into the managerial component than Mohun does). There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (7669.3547) is tautological (equals the source CSV = the final output).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>Mohun 2013, Figure 3 (Supervisory Shares of Total Employment and Total Wages), Section 4.2, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1111,12 +859,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
+          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1128,12 +876,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
+          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1145,12 +893,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
+          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1162,12 +910,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
+          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1179,127 +927,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.5 percent of the "missing" wage and salary accruals are in just six sectors, accounting for 36.1% of total employment, and these sectors are all, in terms of average pay relative to average pay in the whole nonfarm private economy, "richer" sectors of the economy.</t>
+          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Managerial unproductive labor = supervisory labor (managers-plus-capitalists), defined as workers whose function is the authoritarian control and supervision of the working class. Identification criterion: those whose work involves controlling the work of others. Operationally computed as NIPA total employment minus working class (CES production worker) employment, by sector. This subtraction allocates all wages missing from the CES survey — stock options, bonuses, retroactive pay, and other irregular compensation — to supervisory workers. The paper does NOT separately identify capitalists from managers; they are treated together as 'managers-plus-capitalists.'</t>
+          <t>91.5 percent of the "missing" wage and salary accruals are in just six sectors, accounting for 36.1% of total employment, and these sectors are all, in terms of average pay relative to average pay in the whole nonfarm private economy, "richer" sectors of the economy.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.1 and 4.2 and Appendix; full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supervisory employment share of total employment: 1964 = 16.8%; peak 1991 = 19.9%; 2010 = 17.9%. Not a great deal of variation — fluctuates within a 3 percentage point band (after 1973, within 2 points). Supervisory WAGE share of total wages: 1964 = ~32%; 1979 = 35.1%; 1979-1992 = extraordinary increase of ~11 percentage points; peak 2007 = 47.8%; 2010 = 46.6%. This dramatic decoupling of employment share (flat) from wage share (soaring) is the central empirical finding of Mohun (2013).</t>
+          <t>Managerial unproductive labor = supervisory labor (managers-plus-capitalists), defined as workers whose function is the authoritarian control and supervision of the working class. Identification criterion: those whose work involves controlling the work of others. Operationally computed as NIPA total employment minus working class (CES production worker) employment, by sector. This subtraction allocates all wages missing from the CES survey — stock options, bonuses, retroactive pay, and other irregular compensation — to supervisory workers. The paper does NOT separately identify capitalists from managers; they are treated together as 'managers-plus-capitalists.'</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 4.2, Fig 3; full_transcription.md</t>
+          <t>Mohun_2013, Section 2.1 and 4.2 and Appendix; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>value_added_absorption</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supervisory wages as share of money value added (Y): 1964 = 22.1%; 2000 = 35.5% (peak, +60% increase); 2010 = ~34%. Between 1978 and 1992 most of the increase occurred. By 2000, some 13.5 percentage points less of value added was available for working class wages and profits compared to 1964. The entire rise was financed by a fall in the value of labor-power (rise in the rate of surplus value) after 1979 — not at the expense of working class wages (which had a stable VA share), but at the expense of the profit share plus labor-power value.</t>
+          <t>Supervisory employment share of total employment: 1964 = 16.8%; peak 1991 = 19.9%; 2010 = 17.9%. Not a great deal of variation — fluctuates within a 3 percentage point band (after 1973, within 2 points). Supervisory WAGE share of total wages: 1964 = ~32%; 1979 = 35.1%; 1979-1992 = extraordinary increase of ~11 percentage points; peak 2007 = 47.8%; 2010 = 46.6%. This dramatic decoupling of employment share (flat) from wage share (soaring) is the central empirical finding of Mohun (2013).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+          <t>Mohun_2013, Section 4.2, Fig 3; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>class_boundary_definition</t>
+          <t>value_added_absorption</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mohun states: 'In all processes involving capital and wage labor, capitalists hire managers to organize activities and to supervise in order that those activities are satisfactorily performed. These processes are typically hierarchical and authoritarian, with significant pay differentials that increase up the hierarchy. Separating pure organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive... It makes little conceptual sense to say that the policing of the capital relation in production and circulation processes by the agents of capital directly creates value.' Reference to Moseley (1991: 35-6).</t>
+          <t>Supervisory wages as share of money value added (Y): 1964 = 22.1%; 2000 = 35.5% (peak, +60% increase); 2010 = ~34%. Between 1978 and 1992 most of the increase occurred. By 2000, some 13.5 percentage points less of value added was available for working class wages and profits compared to 1964. The entire rise was financed by a fall in the value of labor-power (rise in the rate of surplus value) after 1979 — not at the expense of working class wages (which had a stable VA share), but at the expense of the profit share plus labor-power value.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.1; full_transcription.md</t>
+          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>st_boundary_comparison</t>
+          <t>class_boundary_definition</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>This is the key classification difference between ST and Mohun that drives the XS1404 ratio (ST/Mohun ≈ 1.61). In ST (1994), production workers in service-producing industries are 'nonsupervisory employees' — but in Mining, Manufacturing, and Construction the BLS production worker category additionally excludes finance, trade, personnel, professional, and clerical workers (not just supervisors). Mohun's 2013 framework systematically identifies all supervisory labor across all sectors by subtraction, producing a larger unproductive sector. The 18.7% average supervisory share is what Mohun labels as ST's 'supervision' category — workers absent from the BLS production worker count but not because of sector location, rather because of function.</t>
+          <t>Mohun states: 'In all processes involving capital and wage labor, capitalists hire managers to organize activities and to supervise in order that those activities are satisfactorily performed. These processes are typically hierarchical and authoritarian, with significant pay differentials that increase up the hierarchy. Separating pure organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive... It makes little conceptual sense to say that the policing of the capital relation in production and circulation processes by the agents of capital directly creates value.' Reference to Moseley (1991: 35-6).</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3, Appendix; full_transcription.md; ST_1994 methodology</t>
+          <t>Mohun_2013, Section 2.1; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>st_boundary_comparison</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This is the key classification difference between ST and Mohun that drives the XS1404 ratio (ST/Mohun ≈ 1.61). In ST (1994), production workers in service-producing industries are 'nonsupervisory employees' — but in Mining, Manufacturing, and Construction the BLS production worker category additionally excludes finance, trade, personnel, professional, and clerical workers (not just supervisors). Mohun's 2013 framework systematically identifies all supervisory labor across all sectors by subtraction, producing a larger unproductive sector. The 18.7% average supervisory share is what Mohun labels as ST's 'supervision' category — workers absent from the BLS production worker count but not because of sector location, rather because of function.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 3, Appendix; full_transcription.md; ST_1994 methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>construction_note</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.187', inputs=['Mohun Lu'], output='XS1502-COMBINED'. This reflects the stable 18.7% managerial/supervisory share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Series registry XS1502; Mohun_2013, Section 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D4 REBUILD (2026-07-02): XS1502 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's supervisory (managers-plus-capitalists) share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 3 (p.10/364)). Benchmark values (table/text-grade): 1964=0.168, 1991=0.199, 2010=0.179 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 3 (p.10/364); D4 rebuild</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Managerial/supervisory unproductive employment (Lu_sup = managers-plus-capitalists), 1964-2010. Derived as Mohun total unproductive Lu × 0.187 (stable supervisory share). Employment share flat (~16.8-19.9%). Wage share explodes from 32% (1964) to 47.8% (2007). VA absorption: 22.1% (1964) to 35.5% (2000). This is the category absent from ST's framework but central to Mohun's class analysis and the driver of the ST/Mohun exploitation rate ratio.</t>
+          <t>D4 rebuild anchors (XS1502): 1964=0.168, 1991=0.199, 2010=0.179 (share of total employment). Source = Mohun 2013 Figure 3 (p.10/364), text-reported benchmark values (table/text-grade). These are the primary validation reference values (external, non-tautological). Non-benchmark annual points are figure-grade and were NOT fabricated.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 3 (p.10/364)</t>
         </is>
       </c>
     </row>
@@ -1307,23 +1076,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Managerial/supervisory unproductive employment (Lu_sup = managers-plus-capitalists), 1964-2010. Derived as Mohun total unproductive Lu × 0.187 (stable supervisory share). Employment share flat (~16.8-19.9%). Wage share explodes from 32% (1964) to 47.8% (2007). VA absorption: 22.1% (1964) to 35.5% (2000). This is the category absent from ST's framework but central to Mohun's class analysis and the driver of the ST/Mohun exploitation rate ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CORRECTION (2026-06-11 reconciliation): the registry construction op 'Lu x 0.187' is FABRICATED. The actual data is the Lum_mohun (managerial) column of Mohun's unproductive-employment decomposition (~0.544 of Lu), NOT the 0.187 economy-wide supervisor population share. Data verified correct against source; the registry construction formula must be corrected to a load of Lum_mohun.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supervisory employment computed by subtraction — all CES-missing wages assigned to supervisors, including tips and payments-in-kind that may accrue to working class</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1097,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cannot distinguish capitalists from managers within this aggregate</t>
+          <t>CORRECTION (2026-06-11 reconciliation): the registry construction op 'Lu x 0.187' is FABRICATED. The actual data is the Lum_mohun (managerial) column of Mohun's unproductive-employment decomposition (~0.544 of Lu), NOT the 0.187 economy-wide supervisor population share. Data verified correct against source; the registry construction formula must be corrected to a load of Lum_mohun.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1105,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mining, Manufacturing, Construction 'supervisory' category includes some non-supervisors (finance, clerical, professional workers excluded from BLS production worker definition) — supervisory totals overestimated by indeterminate amount, decreasing as these sectors shrink</t>
+          <t>Supervisory employment computed by subtraction — all CES-missing wages assigned to supervisors, including tips and payments-in-kind that may accrue to working class</t>
         </is>
       </c>
     </row>
@@ -1347,31 +1113,31 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Cannot distinguish capitalists from managers within this aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mining, Manufacturing, Construction 'supervisory' category includes some non-supervisors (finance, clerical, professional workers excluded from BLS production worker definition) — supervisory totals overestimated by indeterminate amount, decreasing as these sectors shrink</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>SIC-to-NAICS transition 1998 requires separate classification tables</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>XS1501</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>XS1503</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1145,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XS1504</t>
+          <t>XS1501</t>
         </is>
       </c>
     </row>
@@ -1387,49 +1153,65 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
+          <t>XS1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>XS1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>XS1404</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Mohun_2013</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Mohun_2013</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1452,7 +1234,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1489,24 +1271,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>derive</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mohun Lu</t>
-        </is>
-      </c>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1502-COMBINED</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Lu — 0.187</t>
-        </is>
-      </c>
+          <t>XS1502-A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -1538,7 +1312,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 7669.3547}</t>
+          <t>{"1964": 0.168, "1991": 0.199, "2010": 0.179}</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1324,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[5000, 50000]</t>
+          <t>[0.14, 0.22]</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1336,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1348,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1502.xlsx
+++ b/extenbooks/XS1502.xlsx
@@ -734,7 +734,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+          <t>&gt; predecessor-build decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_predecessor-build/).</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes supervisory (managers-plus-capitalists) unproductive labor ONLY as SHARES (Figure 3), never as a year-by-year FTE-level table. Verbatim published anchors: supervisory EMPLOYMENT share 1964 = 16.8% of total employment, peak 1991 = 19.9%, 2010 = 17.9%; WAGE share 1964 = ~32% of total wages, peak 2007 = 47.8%, 2010 = 46.6%. HONESTY NOTE: the shipped XS1502 series (source column Lum_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 supervisory / total-employment ratio is 24.4%, which does NOT reproduce Mohun's published 16.8% (the shipped split puts far more of Lu into the managerial component than Mohun does). There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (7669.3547) is tautological (equals the source CSV = the final output).</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes supervisory (managers-plus-capitalists) unproductive labor ONLY as SHARES (Figure 3), never as a year-by-year FTE-level table. Verbatim published anchors: supervisory EMPLOYMENT share 1964 = 16.8% of total employment, peak 1991 = 19.9%, 2010 = 17.9%; WAGE share 1964 = ~32% of total wages, peak 2007 = 47.8%, 2010 = 46.6%. HONESTY NOTE: the shipped XS1502 series (source column Lum_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (predecessor-build) backward decomposition. Its 1964 supervisory / total-employment ratio is 24.4%, which does NOT reproduce Mohun's published 16.8% (the shipped split puts far more of Lu into the managerial component than Mohun does). There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (7669.3547) is tautological (equals the source CSV = the final output).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D4 REBUILD (2026-07-02): XS1502 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's supervisory (managers-plus-capitalists) share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 3 (p.10/364)). Benchmark values (table/text-grade): 1964=0.168, 1991=0.199, 2010=0.179 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+          <t>D4 REBUILD (2026-07-02): XS1502 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's supervisory (managers-plus-capitalists) share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 3 (p.10/364)). Benchmark values (table/text-grade): 1964=0.168, 1991=0.199, 2010=0.179 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled predecessor-build decomposition (DIV-050), retained as a variant arm (chopped/_variants_predecessor-build/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
